--- a/output/2026-09-01_21_Italia_Marche_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-01_21_Italia_Marche_Impiantistica_aspirazione_industriale.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Attiva dal 1974, +45 anni esperienza</t>
+          <t>Attiva dal 1974, +45 anni esperienza [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -540,7 +540,6 @@
           <t>346 8566919</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Ditta individuale (P.IVA 02174560413)</t>
@@ -578,7 +577,6 @@
           <t>0721 270233 / 328 1090971</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Ditta individuale (P.IVA 01240070415)</t>
@@ -616,10 +614,9 @@
           <t>0721 499043</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Attiva dal 1981</t>
+          <t>Attiva dal 1981 [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -661,7 +658,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Attiva dal 1984; dominio email confermato collegato a Barucca Impianti</t>
+          <t>Attiva dal 1984; dominio email confermato collegato a Barucca Impianti [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -696,7 +693,6 @@
           <t>0721 743064</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>40 dipendenti, certificata EN-1090, membro Confapi Pesaro Urbino</t>
@@ -734,10 +730,9 @@
           <t>0733 579790</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Attiva dal 1968; possibile gruppo familiare con Fratelli Giuliodori Srl e Giuliodori Roberto Srl</t>
+          <t>Attiva dal 1968; possibile gruppo familiare con Fratelli Giuliodori Srl e Giuliodori Roberto Srl [DUPLICATO — vedi anche: 2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -779,7 +774,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Attiva da 50 anni; stesso gruppo familiare Giuliodori</t>
+          <t>Attiva da 50 anni; stesso gruppo familiare Giuliodori [DUPLICATO — vedi anche: 2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -794,7 +789,6 @@
           <t>Giuliodori Roberto Srl</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Macerata (Appignano)</t>
@@ -810,10 +804,9 @@
           <t>0733 400050</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nessun sito proprio trovato; presenza su directory; stesso gruppo familiare Giuliodori</t>
+          <t>Nessun sito proprio trovato; presenza su directory; stesso gruppo familiare Giuliodori [DUPLICATO — vedi anche: 2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -855,7 +848,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Attiva dal 2007; opera anche su MC, PE, AQ, TE</t>
+          <t>Attiva dal 2007; opera anche su MC, PE, AQ, TE [DUPLICATO — vedi anche: 2026-09-01_20_Italia_Marche_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -890,7 +883,6 @@
           <t>0736 42510</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Clienti confermati: industrie manifatturiere, plastica, alimentare, farmaceutico</t>
